--- a/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
+++ b/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60E144F-DF0E-438C-B337-7FA90B2D16B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D411B01D-F003-4B42-B27A-EBD896E03DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitBack" sheetId="1" r:id="rId1"/>
@@ -862,7 +862,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -871,8 +871,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -887,6 +894,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -920,17 +932,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -947,9 +962,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -987,9 +1002,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1022,9 +1037,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1057,9 +1089,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1234,60 +1283,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1613,7 +1662,7 @@
       </c>
       <c r="BB2" s="2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>263</v>
       </c>
@@ -1776,7 +1825,7 @@
       </c>
       <c r="BB3" s="2"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>59</v>
       </c>
@@ -1939,7 +1988,7 @@
       </c>
       <c r="BB4" s="2"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2102,7 +2151,7 @@
       </c>
       <c r="BB5" s="2"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -2265,7 +2314,7 @@
       </c>
       <c r="BB6" s="2"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>65</v>
       </c>
@@ -2428,7 +2477,7 @@
       </c>
       <c r="BB7" s="2"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>66</v>
       </c>
@@ -2591,7 +2640,7 @@
       </c>
       <c r="BB8" s="2"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
@@ -2754,7 +2803,7 @@
       </c>
       <c r="BB9" s="2"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2917,7 +2966,7 @@
       </c>
       <c r="BB10" s="2"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>71</v>
       </c>
@@ -3080,7 +3129,7 @@
       </c>
       <c r="BB11" s="2"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>73</v>
       </c>
@@ -3243,7 +3292,7 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
@@ -3406,7 +3455,7 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>77</v>
       </c>
@@ -3569,7 +3618,7 @@
       </c>
       <c r="BB14" s="2"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
@@ -3732,7 +3781,7 @@
       </c>
       <c r="BB15" s="2"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>81</v>
       </c>
@@ -3766,8 +3815,8 @@
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>49</v>
+      <c r="L16" s="5">
+        <v>51</v>
       </c>
       <c r="M16" s="3">
         <v>-1</v>
@@ -3895,7 +3944,7 @@
       </c>
       <c r="BB16" s="2"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>83</v>
       </c>
@@ -4058,7 +4107,7 @@
       </c>
       <c r="BB17" s="2"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
@@ -4221,7 +4270,7 @@
       </c>
       <c r="BB18" s="2"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
@@ -4384,7 +4433,7 @@
       </c>
       <c r="BB19" s="2"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>88</v>
       </c>
@@ -4547,7 +4596,7 @@
       </c>
       <c r="BB20" s="2"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>90</v>
       </c>
@@ -4710,7 +4759,7 @@
       </c>
       <c r="BB21" s="2"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>92</v>
       </c>
@@ -4873,7 +4922,7 @@
       </c>
       <c r="BB22" s="2"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>94</v>
       </c>
@@ -5036,7 +5085,7 @@
       </c>
       <c r="BB23" s="2"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>267</v>
       </c>
@@ -5199,7 +5248,7 @@
       </c>
       <c r="BB24" s="2"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>98</v>
       </c>
@@ -5362,7 +5411,7 @@
       </c>
       <c r="BB25" s="2"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>100</v>
       </c>
@@ -5525,7 +5574,7 @@
       </c>
       <c r="BB26" s="2"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>101</v>
       </c>
@@ -5688,7 +5737,7 @@
       </c>
       <c r="BB27" s="2"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>102</v>
       </c>
@@ -5851,7 +5900,7 @@
       </c>
       <c r="BB28" s="2"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>104</v>
       </c>
@@ -6014,7 +6063,7 @@
       </c>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>106</v>
       </c>
@@ -6177,7 +6226,7 @@
       </c>
       <c r="BB30" s="2"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>108</v>
       </c>
@@ -6340,7 +6389,7 @@
       </c>
       <c r="BB31" s="2"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>110</v>
       </c>
@@ -6503,7 +6552,7 @@
       </c>
       <c r="BB32" s="2"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>112</v>
       </c>
@@ -6666,7 +6715,7 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>114</v>
       </c>
@@ -6829,7 +6878,7 @@
       </c>
       <c r="BB34" s="2"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>116</v>
       </c>
@@ -6992,7 +7041,7 @@
       </c>
       <c r="BB35" s="2"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>118</v>
       </c>
@@ -7155,7 +7204,7 @@
       </c>
       <c r="BB36" s="2"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>120</v>
       </c>
@@ -7189,8 +7238,8 @@
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
-        <v>49</v>
+      <c r="L37" s="5">
+        <v>51</v>
       </c>
       <c r="M37" s="3">
         <v>-1</v>
@@ -7318,7 +7367,7 @@
       </c>
       <c r="BB37" s="2"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>122</v>
       </c>
@@ -7481,7 +7530,7 @@
       </c>
       <c r="BB38" s="2"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>124</v>
       </c>
@@ -7644,7 +7693,7 @@
       </c>
       <c r="BB39" s="2"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>126</v>
       </c>
@@ -7807,7 +7856,7 @@
       </c>
       <c r="BB40" s="2"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>127</v>
       </c>
@@ -7970,7 +8019,7 @@
       </c>
       <c r="BB41" s="2"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>129</v>
       </c>
@@ -8133,7 +8182,7 @@
       </c>
       <c r="BB42" s="2"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>131</v>
       </c>
@@ -8296,7 +8345,7 @@
       </c>
       <c r="BB43" s="2"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>133</v>
       </c>
@@ -8459,7 +8508,7 @@
       </c>
       <c r="BB44" s="2"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>270</v>
       </c>
@@ -8622,7 +8671,7 @@
       </c>
       <c r="BB45" s="2"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>137</v>
       </c>
@@ -8785,7 +8834,7 @@
       </c>
       <c r="BB46" s="2"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>139</v>
       </c>
@@ -8948,7 +8997,7 @@
       </c>
       <c r="BB47" s="2"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>141</v>
       </c>
@@ -9111,7 +9160,7 @@
       </c>
       <c r="BB48" s="2"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>143</v>
       </c>
@@ -9274,7 +9323,7 @@
       </c>
       <c r="BB49" s="2"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>145</v>
       </c>
@@ -9437,7 +9486,7 @@
       </c>
       <c r="BB50" s="2"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>147</v>
       </c>
@@ -9600,7 +9649,7 @@
       </c>
       <c r="BB51" s="2"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>149</v>
       </c>
@@ -9763,7 +9812,7 @@
       </c>
       <c r="BB52" s="2"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>151</v>
       </c>
@@ -9926,7 +9975,7 @@
       </c>
       <c r="BB53" s="2"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>153</v>
       </c>
@@ -10089,7 +10138,7 @@
       </c>
       <c r="BB54" s="2"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>155</v>
       </c>
@@ -10252,7 +10301,7 @@
       </c>
       <c r="BB55" s="2"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>157</v>
       </c>
@@ -10415,7 +10464,7 @@
       </c>
       <c r="BB56" s="2"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>159</v>
       </c>
@@ -10578,7 +10627,7 @@
       </c>
       <c r="BB57" s="2"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>161</v>
       </c>
@@ -10741,7 +10790,7 @@
       </c>
       <c r="BB58" s="2"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>163</v>
       </c>
@@ -10904,7 +10953,7 @@
       </c>
       <c r="BB59" s="2"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>165</v>
       </c>
@@ -11067,7 +11116,7 @@
       </c>
       <c r="BB60" s="2"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>167</v>
       </c>
@@ -11230,7 +11279,7 @@
       </c>
       <c r="BB61" s="2"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>169</v>
       </c>
@@ -11393,7 +11442,7 @@
       </c>
       <c r="BB62" s="2"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>171</v>
       </c>
@@ -11556,7 +11605,7 @@
       </c>
       <c r="BB63" s="2"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>173</v>
       </c>
@@ -11719,7 +11768,7 @@
       </c>
       <c r="BB64" s="2"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>175</v>
       </c>
@@ -11882,7 +11931,7 @@
       </c>
       <c r="BB65" s="2"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>177</v>
       </c>
@@ -12045,7 +12094,7 @@
       </c>
       <c r="BB66" s="2"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>180</v>
       </c>
@@ -12208,7 +12257,7 @@
       </c>
       <c r="BB67" s="2"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>182</v>
       </c>
@@ -12371,7 +12420,7 @@
       </c>
       <c r="BB68" s="2"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>184</v>
       </c>
@@ -12534,7 +12583,7 @@
       </c>
       <c r="BB69" s="2"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>186</v>
       </c>
@@ -12697,7 +12746,7 @@
       </c>
       <c r="BB70" s="2"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>188</v>
       </c>
@@ -12860,7 +12909,7 @@
       </c>
       <c r="BB71" s="2"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>190</v>
       </c>
@@ -13023,7 +13072,7 @@
       </c>
       <c r="BB72" s="2"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>192</v>
       </c>
@@ -13186,7 +13235,7 @@
       </c>
       <c r="BB73" s="2"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>194</v>
       </c>
@@ -13349,7 +13398,7 @@
       </c>
       <c r="BB74" s="2"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>196</v>
       </c>
@@ -13512,7 +13561,7 @@
       </c>
       <c r="BB75" s="2"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>198</v>
       </c>
@@ -13675,7 +13724,7 @@
       </c>
       <c r="BB76" s="2"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>200</v>
       </c>
@@ -13838,7 +13887,7 @@
       </c>
       <c r="BB77" s="2"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>202</v>
       </c>
@@ -14001,7 +14050,7 @@
       </c>
       <c r="BB78" s="2"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>204</v>
       </c>
@@ -14164,7 +14213,7 @@
       </c>
       <c r="BB79" s="2"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>206</v>
       </c>
@@ -14327,7 +14376,7 @@
       </c>
       <c r="BB80" s="2"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>208</v>
       </c>
@@ -14490,7 +14539,7 @@
       </c>
       <c r="BB81" s="2"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>210</v>
       </c>
@@ -14653,7 +14702,7 @@
       </c>
       <c r="BB82" s="2"/>
     </row>
-    <row r="83" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>212</v>
       </c>
@@ -14816,7 +14865,7 @@
       </c>
       <c r="BB83" s="2"/>
     </row>
-    <row r="84" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>214</v>
       </c>
@@ -14979,7 +15028,7 @@
       </c>
       <c r="BB84" s="2"/>
     </row>
-    <row r="85" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>216</v>
       </c>
@@ -15142,7 +15191,7 @@
       </c>
       <c r="BB85" s="2"/>
     </row>
-    <row r="86" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>218</v>
       </c>
@@ -15314,56 +15363,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BD86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="51" max="52" width="7" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>220</v>
       </c>
@@ -15533,7 +15582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitBack!A2</f>
         <v>Code</v>
@@ -15728,7 +15777,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitBack!A3</f>
         <v>unb0006</v>
@@ -15923,7 +15972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitBack!A4</f>
         <v>unba001</v>
@@ -16118,7 +16167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitBack!A5</f>
         <v>unba002</v>
@@ -16313,7 +16362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitBack!A6</f>
         <v>unba003</v>
@@ -16508,7 +16557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitBack!A7</f>
         <v>unba004</v>
@@ -16703,7 +16752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitBack!A8</f>
         <v>unba005</v>
@@ -16898,7 +16947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitBack!A9</f>
         <v>unba006</v>
@@ -17093,7 +17142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitBack!A10</f>
         <v>unba007</v>
@@ -17288,7 +17337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitBack!A11</f>
         <v>unba008</v>
@@ -17483,7 +17532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitBack!A12</f>
         <v>unba009</v>
@@ -17678,7 +17727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitBack!A13</f>
         <v>unba010</v>
@@ -17873,7 +17922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitBack!A14</f>
         <v>unba011</v>
@@ -18068,7 +18117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitBack!A15</f>
         <v>unba012</v>
@@ -18263,7 +18312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitBack!A16</f>
         <v>unba013</v>
@@ -18403,7 +18452,7 @@
       </c>
       <c r="AO16">
         <f>UnitBack!L16</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitBack!N16</f>
@@ -18458,7 +18507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitBack!A17</f>
         <v>unba014</v>
@@ -18653,7 +18702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitBack!A18</f>
         <v>unba015</v>
@@ -18848,7 +18897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitBack!A19</f>
         <v>unba016</v>
@@ -19043,7 +19092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitBack!A20</f>
         <v>unba017</v>
@@ -19238,7 +19287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitBack!A21</f>
         <v>unba018</v>
@@ -19433,7 +19482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitBack!A22</f>
         <v>unba019</v>
@@ -19628,7 +19677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitBack!A23</f>
         <v>unba020</v>
@@ -19823,7 +19872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitBack!A24</f>
         <v>unb0002</v>
@@ -20018,7 +20067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitBack!A25</f>
         <v>unba021</v>
@@ -20213,7 +20262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitBack!A26</f>
         <v>unba022</v>
@@ -20408,7 +20457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitBack!A27</f>
         <v>unba023</v>
@@ -20603,7 +20652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitBack!A28</f>
         <v>unba024</v>
@@ -20798,7 +20847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitBack!A29</f>
         <v>unba025</v>
@@ -20993,7 +21042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitBack!A30</f>
         <v>unba026</v>
@@ -21188,7 +21237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitBack!A31</f>
         <v>unba027</v>
@@ -21383,7 +21432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitBack!A32</f>
         <v>unba028</v>
@@ -21578,7 +21627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitBack!A33</f>
         <v>unba029</v>
@@ -21773,7 +21822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitBack!A34</f>
         <v>unba030</v>
@@ -21968,7 +22017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitBack!A35</f>
         <v>unba031</v>
@@ -22163,7 +22212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitBack!A36</f>
         <v>unba032</v>
@@ -22358,7 +22407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitBack!A37</f>
         <v>unba033</v>
@@ -22498,7 +22547,7 @@
       </c>
       <c r="AO37">
         <f>UnitBack!L37</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitBack!N37</f>
@@ -22553,7 +22602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitBack!A38</f>
         <v>unba034</v>
@@ -22748,7 +22797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitBack!A39</f>
         <v>unba035</v>
@@ -22943,7 +22992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitBack!A40</f>
         <v>unba036</v>
@@ -23138,7 +23187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitBack!A41</f>
         <v>unba037</v>
@@ -23333,7 +23382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitBack!A42</f>
         <v>unba038</v>
@@ -23528,7 +23577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitBack!A43</f>
         <v>unba039</v>
@@ -23723,7 +23772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitBack!A44</f>
         <v>unba040</v>
@@ -23918,7 +23967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitBack!A45</f>
         <v>unb0004</v>
@@ -24113,7 +24162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitBack!A46</f>
         <v>unba041</v>
@@ -24308,7 +24357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitBack!A47</f>
         <v>unba042</v>
@@ -24503,7 +24552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitBack!A48</f>
         <v>unba043</v>
@@ -24698,7 +24747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitBack!A49</f>
         <v>unba044</v>
@@ -24893,7 +24942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitBack!A50</f>
         <v>unba045</v>
@@ -25088,7 +25137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitBack!A51</f>
         <v>unba046</v>
@@ -25283,7 +25332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitBack!A52</f>
         <v>unba047</v>
@@ -25478,7 +25527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitBack!A53</f>
         <v>unba048</v>
@@ -25673,7 +25722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitBack!A54</f>
         <v>unba049</v>
@@ -25868,7 +25917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitBack!A55</f>
         <v>unba050</v>
@@ -26063,7 +26112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitBack!A56</f>
         <v>unba051</v>
@@ -26258,7 +26307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitBack!A57</f>
         <v>unba052</v>
@@ -26453,7 +26502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitBack!A58</f>
         <v>unba053</v>
@@ -26648,7 +26697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitBack!A59</f>
         <v>unba054</v>
@@ -26843,7 +26892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitBack!A60</f>
         <v>unba055</v>
@@ -27038,7 +27087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitBack!A61</f>
         <v>unba056</v>
@@ -27233,7 +27282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitBack!A62</f>
         <v>unba057</v>
@@ -27428,7 +27477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitBack!A63</f>
         <v>unba058</v>
@@ -27623,7 +27672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitBack!A64</f>
         <v>unba059</v>
@@ -27818,7 +27867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitBack!A65</f>
         <v>unba060</v>
@@ -28013,7 +28062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitBack!A66</f>
         <v>unbn000</v>
@@ -28208,7 +28257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitBack!A67</f>
         <v>unba061</v>
@@ -28403,7 +28452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitBack!A68</f>
         <v>unba062</v>
@@ -28598,7 +28647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitBack!A69</f>
         <v>unba063</v>
@@ -28793,7 +28842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitBack!A70</f>
         <v>unba064</v>
@@ -28988,7 +29037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitBack!A71</f>
         <v>unba065</v>
@@ -29183,7 +29232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitBack!A72</f>
         <v>unba066</v>
@@ -29378,7 +29427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitBack!A73</f>
         <v>unba067</v>
@@ -29573,7 +29622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitBack!A74</f>
         <v>unba068</v>
@@ -29768,7 +29817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitBack!A75</f>
         <v>unba069</v>
@@ -29963,7 +30012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitBack!A76</f>
         <v>unba070</v>
@@ -30158,7 +30207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitBack!A77</f>
         <v>unba071</v>
@@ -30353,7 +30402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitBack!A78</f>
         <v>unba072</v>
@@ -30548,7 +30597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitBack!A79</f>
         <v>unba073</v>
@@ -30743,7 +30792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitBack!A80</f>
         <v>unba074</v>
@@ -30938,7 +30987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitBack!A81</f>
         <v>unba075</v>
@@ -31133,7 +31182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitBack!A82</f>
         <v>unba076</v>
@@ -31328,7 +31377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
         <f>UnitBack!A83</f>
         <v>unba077</v>
@@ -31523,7 +31572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
         <f>UnitBack!A84</f>
         <v>unba078</v>
@@ -31718,7 +31767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
         <f>UnitBack!A85</f>
         <v>unba079</v>
@@ -31913,7 +31962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
         <f>UnitBack!A86</f>
         <v>unba080</v>
@@ -32117,9 +32166,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -32130,7 +32179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>225</v>
       </c>
@@ -32139,7 +32188,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -32148,7 +32197,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -32157,7 +32206,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -32166,7 +32215,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -32175,7 +32224,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -32184,7 +32233,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -32193,7 +32242,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -32202,7 +32251,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -32211,7 +32260,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -32220,7 +32269,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -32229,7 +32278,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -32238,7 +32287,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -32247,7 +32296,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -32256,7 +32305,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -32265,7 +32314,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -32274,7 +32323,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -32283,7 +32332,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -32292,7 +32341,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -32301,7 +32350,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -32310,7 +32359,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -32319,7 +32368,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -32328,7 +32377,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -32337,7 +32386,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -32346,7 +32395,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -32355,7 +32404,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -32364,7 +32413,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -32373,7 +32422,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -32382,7 +32431,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -32391,7 +32440,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -32400,7 +32449,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -32409,7 +32458,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -32418,7 +32467,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -32427,7 +32476,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -32436,7 +32485,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -32445,7 +32494,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -32454,7 +32503,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -32463,7 +32512,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -32472,7 +32521,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -32481,7 +32530,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -32490,7 +32539,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -32499,7 +32548,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -32508,7 +32557,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -32517,7 +32566,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -32526,7 +32575,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -32535,7 +32584,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -32544,7 +32593,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -32553,7 +32602,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -32562,7 +32611,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -32571,7 +32620,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -32580,7 +32629,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -32589,7 +32638,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -32598,7 +32647,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -32607,7 +32656,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -32616,7 +32665,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -32625,7 +32674,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -32634,7 +32683,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -32643,7 +32692,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -32652,7 +32701,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -32661,7 +32710,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -32670,7 +32719,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -32679,7 +32728,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -32688,7 +32737,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -32697,7 +32746,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -32706,7 +32755,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -32715,7 +32764,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -32724,7 +32773,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -32733,7 +32782,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -32742,7 +32791,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -32751,7 +32800,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -32760,7 +32809,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -32769,7 +32818,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -32778,7 +32827,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -32787,7 +32836,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -32796,7 +32845,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -32805,7 +32854,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -32814,7 +32863,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -32823,7 +32872,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -32832,7 +32881,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -32841,7 +32890,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -32850,7 +32899,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>
@@ -32859,7 +32908,7 @@
       </c>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>80</v>
       </c>
@@ -32868,7 +32917,7 @@
       </c>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>81</v>
       </c>
@@ -32877,7 +32926,7 @@
       </c>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>82</v>
       </c>
@@ -32886,7 +32935,7 @@
       </c>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>83</v>
       </c>
@@ -32895,7 +32944,7 @@
       </c>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>84</v>
       </c>

--- a/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
+++ b/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D411B01D-F003-4B42-B27A-EBD896E03DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71CDF1B-12F9-461D-A217-B1E5230DE9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -878,8 +878,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -899,6 +906,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -932,20 +944,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6715,168 +6732,168 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:54" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>7</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="6">
         <v>5</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="G34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
         <v>41</v>
       </c>
-      <c r="M34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="3">
-        <v>2</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="M34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>2</v>
+      </c>
+      <c r="O34" s="6">
         <v>80</v>
       </c>
-      <c r="P34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="2">
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
         <v>1</v>
       </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2">
-        <v>0</v>
-      </c>
-      <c r="U34" s="2">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2">
-        <v>0</v>
-      </c>
-      <c r="W34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="2">
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="7">
+        <v>0</v>
+      </c>
+      <c r="U34" s="7">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="X34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7">
         <v>50</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="7">
         <v>50</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AB34" s="6">
         <v>85</v>
       </c>
-      <c r="AC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
+      <c r="AC34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
         <v>1000000</v>
       </c>
-      <c r="AK34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="3">
+      <c r="AK34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="2">
+      <c r="AM34" s="7">
         <v>20000</v>
       </c>
-      <c r="AN34" s="3">
-        <v>100</v>
-      </c>
-      <c r="AO34" s="3">
-        <v>2</v>
-      </c>
-      <c r="AP34" s="3">
+      <c r="AN34" s="6">
+        <v>100</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>2</v>
+      </c>
+      <c r="AP34" s="6">
         <v>4</v>
       </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="2" t="str">
+      <c r="AQ34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>tunba030</v>
       </c>
-      <c r="AZ34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA34" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="2"/>
+      <c r="AZ34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BA34" s="6">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="7"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">

--- a/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
+++ b/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71CDF1B-12F9-461D-A217-B1E5230DE9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A5A863-273F-4FA1-B960-E71101308EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,7 +949,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -959,6 +959,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -6838,8 +6839,8 @@
       <c r="AI34" s="6">
         <v>0</v>
       </c>
-      <c r="AJ34" s="6">
-        <v>1000000</v>
+      <c r="AJ34" s="9">
+        <v>90909382</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -21871,7 +21872,7 @@
       </c>
       <c r="I34">
         <f>UnitBack!AJ34</f>
-        <v>1000000</v>
+        <v>90909382</v>
       </c>
       <c r="J34">
         <f>UnitBack!AK34</f>

--- a/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
+++ b/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A5A863-273F-4FA1-B960-E71101308EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59F12FF-EED3-48F5-8688-51414E411E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitBack" sheetId="1" r:id="rId1"/>
@@ -886,7 +886,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -911,6 +911,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -949,7 +955,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -960,6 +966,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -980,9 +989,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1020,9 +1029,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1055,26 +1064,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1107,26 +1099,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3310,168 +3285,168 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="10">
         <v>3</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="10">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
+      <c r="G13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
         <v>41</v>
       </c>
-      <c r="M13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N13" s="3">
-        <v>2</v>
-      </c>
-      <c r="O13" s="3">
+      <c r="M13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>2</v>
+      </c>
+      <c r="O13" s="10">
         <v>80</v>
       </c>
-      <c r="P13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R13" s="2">
+      <c r="P13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="R13" s="11">
         <v>1</v>
       </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="2">
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
+      <c r="V13" s="11">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="X13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="11">
         <v>50</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AA13" s="11">
         <v>50</v>
       </c>
-      <c r="AB13" s="3">
-        <v>125</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="AK13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="3">
+      <c r="AB13" s="10">
+        <v>105</v>
+      </c>
+      <c r="AC13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="11">
+        <v>-1</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>900000</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
         <v>1</v>
       </c>
-      <c r="AM13" s="2">
-        <v>20000</v>
-      </c>
-      <c r="AN13" s="3">
+      <c r="AM13" s="9">
+        <v>90000</v>
+      </c>
+      <c r="AN13" s="10">
         <v>500</v>
       </c>
-      <c r="AO13" s="3">
+      <c r="AO13" s="10">
         <v>3</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AP13" s="10">
         <v>8</v>
       </c>
-      <c r="AQ13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="2" t="str">
+      <c r="AQ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>tunba010</v>
       </c>
-      <c r="AZ13" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA13" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB13" s="2"/>
+      <c r="AZ13" s="10">
+        <v>-1</v>
+      </c>
+      <c r="BA13" s="10">
+        <v>2</v>
+      </c>
+      <c r="BB13" s="11"/>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
@@ -6840,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="9">
-        <v>90909382</v>
+        <v>900000</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -6848,8 +6823,8 @@
       <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
-        <v>20000</v>
+      <c r="AM34" s="9">
+        <v>90000</v>
       </c>
       <c r="AN34" s="6">
         <v>100</v>
@@ -17777,7 +17752,7 @@
       </c>
       <c r="I13">
         <f>UnitBack!AJ13</f>
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="J13">
         <f>UnitBack!AK13</f>
@@ -17839,7 +17814,7 @@
       </c>
       <c r="AB13">
         <f>UnitBack!AB13</f>
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="AC13">
         <f>UnitBack!AE13</f>
@@ -21872,7 +21847,7 @@
       </c>
       <c r="I34">
         <f>UnitBack!AJ34</f>
-        <v>90909382</v>
+        <v>900000</v>
       </c>
       <c r="J34">
         <f>UnitBack!AK34</f>

--- a/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
+++ b/gu_in/Item.edf/42_UnitBack/UnitBack.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59F12FF-EED3-48F5-8688-51414E411E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6FF1F-A150-4605-BA1A-B9F4F90B34D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitBack" sheetId="1" r:id="rId1"/>
@@ -989,9 +989,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1029,9 +1029,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1064,9 +1064,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1099,9 +1116,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6815,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="9">
-        <v>900000</v>
+        <v>1800000</v>
       </c>
       <c r="AK34" s="6">
         <v>0</v>
@@ -6824,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="9">
-        <v>90000</v>
+        <v>909091</v>
       </c>
       <c r="AN34" s="6">
         <v>100</v>
@@ -21847,7 +21881,7 @@
       </c>
       <c r="I34">
         <f>UnitBack!AJ34</f>
-        <v>900000</v>
+        <v>1800000</v>
       </c>
       <c r="J34">
         <f>UnitBack!AK34</f>
